--- a/documents/gkill_user_document.xlsx
+++ b/documents/gkill_user_document.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamat\Git\gkill\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07962EA9-173F-4941-AA5B-86B695DA4284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7E1C67-4E7F-413B-ACD3-0045391F42E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{231E213C-47DE-4CA2-9B9F-8072DD02A1E6}"/>
   </bookViews>
   <sheets>
-    <sheet name="利用ガイド" sheetId="1" r:id="rId1"/>
-    <sheet name="QA" sheetId="3" r:id="rId2"/>
+    <sheet name="導入" sheetId="6" r:id="rId1"/>
+    <sheet name="利用ガイド" sheetId="1" r:id="rId2"/>
+    <sheet name="QA" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">導入!$A$1:$AG$49</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
   <si>
     <t>最終更新日時：2025/11/15 15:45</t>
     <rPh sb="0" eb="4">
@@ -1023,13 +1027,131 @@
   </si>
   <si>
     <t>対象についての分析結果を、日本語の文書にて詳細にお願いします。</t>
+  </si>
+  <si>
+    <t>gkill 導入</t>
+    <rPh sb="6" eb="8">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>わたしは、記録がすきです。</t>
+  </si>
+  <si>
+    <t>一旦おいておいてあとから熟考したり、見返して懐かしんだり。諸々を豊かにしてくれるからです。</t>
+  </si>
+  <si>
+    <t>なんとなくですが、「記録」によって'よくなっている'気がします。</t>
+  </si>
+  <si>
+    <t>そんな記録好きの私ですが、gkillというライフログアプリケーションを作成しました。</t>
+  </si>
+  <si>
+    <t>今回は売り込みをさせてください！</t>
+  </si>
+  <si>
+    <t>3つの特徴からご紹介します！</t>
+  </si>
+  <si>
+    <t>★速攻の記録</t>
+  </si>
+  <si>
+    <t>　記録操作は、'いいかんじ'にするための手段であり通過地点です。</t>
+  </si>
+  <si>
+    <t>　サクっと記録しちゃいましょう！消えないうちに、「有」らせることだけ！</t>
+  </si>
+  <si>
+    <t>　・ボタン1つで記録できます！</t>
+  </si>
+  <si>
+    <t>　・Enterキー1回でメモ帳を起動できます！</t>
+  </si>
+  <si>
+    <t>　・キーボードだけで記録できます！（保存ボタンに腕を運ばなくてOK！）</t>
+  </si>
+  <si>
+    <t>★「景色」、「状況」とgkillでの検索</t>
+  </si>
+  <si>
+    <t>　gkillは「景色」を意識して開発しました。</t>
+  </si>
+  <si>
+    <t>　「去年の夏、新宿で友人Aとカフェで仕事について話をしたな～、とてもたのしかった」みたいな、景色。</t>
+  </si>
+  <si>
+    <t>　場所はこのあたり！友人Aといたとき！など「状況の一部」があれば、記録にたどり着くことができます！</t>
+  </si>
+  <si>
+    <t>　また、その記録から「景色」の想起を助けます！</t>
+  </si>
+  <si>
+    <t>　（もちろん、日時やキーワードからも探すことができますよ～）</t>
+  </si>
+  <si>
+    <t>★集計と分析</t>
+  </si>
+  <si>
+    <t>　gkillには簡単な集計機能があります。</t>
+  </si>
+  <si>
+    <t>　あなたの興味に合わせてカスタマイズしてください！</t>
+  </si>
+  <si>
+    <t>　また、もっとくわしく分析したいときもあると思います。</t>
+  </si>
+  <si>
+    <t>　そのときはAIに分析依頼できます！</t>
+  </si>
+  <si>
+    <t>　それ用のファイルを出力できます！</t>
+  </si>
+  <si>
+    <t>★gkill</t>
+  </si>
+  <si>
+    <t>　実際の感覚は、こちらから体験できます。</t>
+  </si>
+  <si>
+    <t>　サンプルの旅行記録です。もしよければためしてみてください！</t>
+  </si>
+  <si>
+    <t>　旅行サンプル記録：https://github.com/mt3hr/gkill/releases/download/v1.0.8/gkill_sample_data_v1.0.8.zip</t>
+  </si>
+  <si>
+    <t>　画面の説明　　　：https://github.com/mt3hr/gkill/raw/refs/heads/main/documents/gkill_user_document.xlsx</t>
+  </si>
+  <si>
+    <t>　①「gkill_sample_data_v1.0.8.zip」をクリックしてダウンロード</t>
+  </si>
+  <si>
+    <t>　②zipファイルを展開</t>
+  </si>
+  <si>
+    <t>　③「LAUNCH_GKILL_SAMPLE_DATA.bat」をダブルクリック</t>
+  </si>
+  <si>
+    <t>　④「ユーザ名：gkill_sample_data」「パスワード：sample」でログインできます！</t>
+  </si>
+  <si>
+    <t>さいごに。</t>
+  </si>
+  <si>
+    <t>すべての記録はあなただけが見れます。安心してください。</t>
+  </si>
+  <si>
+    <t>もし不具合があればこちらにご連絡ください。</t>
+  </si>
+  <si>
+    <t>ymt3shr@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1083,6 +1205,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1118,7 +1248,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1144,6 +1274,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,8 +1306,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>86436</xdr:rowOff>
     </xdr:to>
@@ -1217,8 +1350,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>89815</xdr:rowOff>
     </xdr:to>
@@ -1261,8 +1394,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>86061</xdr:rowOff>
     </xdr:to>
@@ -1305,8 +1438,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>89632</xdr:rowOff>
     </xdr:to>
@@ -1349,8 +1482,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>86062</xdr:rowOff>
     </xdr:to>
@@ -1393,8 +1526,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>256725</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>2725</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>89816</xdr:rowOff>
     </xdr:to>
@@ -1701,8 +1834,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>256275</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>2275</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>1875</xdr:rowOff>
     </xdr:to>
@@ -1745,8 +1878,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>256275</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>2275</xdr:colOff>
       <xdr:row>51</xdr:row>
       <xdr:rowOff>179632</xdr:rowOff>
     </xdr:to>
@@ -1789,8 +1922,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>256274</xdr:colOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>2274</xdr:colOff>
       <xdr:row>104</xdr:row>
       <xdr:rowOff>1875</xdr:rowOff>
     </xdr:to>
@@ -2584,7 +2717,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC493F5-D12B-45E2-9B82-72B80CF1F903}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:AC49"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="702" width="3.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="703" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:29" ht="35.25" x14ac:dyDescent="0.4">
+      <c r="B1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="AC2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="AC3" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B4" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B5" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B6" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B8" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B9" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B10" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B12" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B13" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B14" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B16" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B17" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B20" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B21" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B23" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B24" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B25" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B29" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B32" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B36" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B37" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B39" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B40" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B41" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B42" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B43" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B44" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B46" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B47" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B48" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B49" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="70" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="69" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A64BFFB2-3335-42E1-BD0E-ACD6D1FF0915}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:AS266"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3105,8 +3464,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="34" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <rowBreaks count="6" manualBreakCount="6">
+    <brk id="52" max="16383" man="1"/>
+    <brk id="86" max="16383" man="1"/>
+    <brk id="124" max="16383" man="1"/>
+    <brk id="163" max="16383" man="1"/>
+    <brk id="187" max="16383" man="1"/>
+    <brk id="239" max="16383" man="1"/>
+  </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="69" man="1"/>
   </colBreaks>
@@ -3114,7 +3481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F0C4C1-0883-401B-87BA-247F49FE07BA}">
   <dimension ref="B1:AS10"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/documents/gkill_user_document.xlsx
+++ b/documents/gkill_user_document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamat\Git\gkill\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7E1C67-4E7F-413B-ACD3-0045391F42E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4295784-08AA-442D-91B1-5F7B6B3FFD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{231E213C-47DE-4CA2-9B9F-8072DD02A1E6}"/>
   </bookViews>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">導入!$A$1:$AG$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">利用ガイド!$A$1:$AX$425</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="193">
   <si>
     <t>最終更新日時：2025/11/15 15:45</t>
     <rPh sb="0" eb="4">
@@ -624,13 +625,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>KFTL記法</t>
-    <rPh sb="4" eb="6">
-      <t>キホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プロンプト例</t>
     <rPh sb="5" eb="6">
       <t>レイ</t>
@@ -1145,13 +1139,624 @@
   </si>
   <si>
     <t>ymt3shr@gmail.com</t>
+  </si>
+  <si>
+    <t>タグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「、」で複数タグを追加できます。</t>
+    <rPh sb="4" eb="6">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーー」で囲んだ範囲の行は、テキストとなります。</t>
+    <rPh sb="5" eb="6">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「。」を1文字目に入れると、タグ行となります。</t>
+    <rPh sb="5" eb="7">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ帳 記録記法</t>
+    <rPh sb="2" eb="3">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打刻</t>
+    <rPh sb="0" eb="2">
+      <t>ダコク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーた」を記入すると、打刻開始解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダコク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーち」を記入すると、打刻解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダコク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーら」を記入すると、気分値解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キブン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>0～10で記録できます。</t>
+    <rPh sb="5" eb="7">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーか」を記入すると、数値記録解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーん」を記入すると、支出記録解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区切り（「、、」や「、」）を入れるまで、</t>
+    <rPh sb="0" eb="2">
+      <t>クギ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ店に対する支出として記録可能です。</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>区切り、一括記録</t>
+    <rPh sb="0" eb="2">
+      <t>クギ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イッカツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「、、」を入力すると、次の記録を入力できます。</t>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「、」を入力しても、次の記録を入力できます。</t>
+    <rPh sb="4" eb="6">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライフログビューでの表示順が保証されるためです。</t>
+    <rPh sb="10" eb="13">
+      <t>ヒョウジジュン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ホショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前者は記録の日時を1秒すすめます。おすすめです。</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブックマーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーう」を記入すると、ブックマーク解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルが入力されなかった場合、自動取得を試みます。</t>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>ジドウシュトク</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ココロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーみ」を記入すると、タスク解釈が始まります。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カイシャク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>板名が記入されなかった場合、設定の「デフォルト板名」が適用されます。</t>
+    <rPh sb="0" eb="1">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保存</t>
+    <rPh sb="0" eb="2">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「！」を末尾に記載し、「Enterキー」を押すと保存されます。</t>
+    <rPh sb="4" eb="6">
+      <t>マツビ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ただし、タグとテキストは適用されません。</t>
+    <rPh sb="12" eb="14">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打刻終了</t>
+    <rPh sb="0" eb="2">
+      <t>ダコク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーたえ」を記入すると、打刻を終了できます。タグで対象を指定、対象がない場合は失敗します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーいえ」を記入すると、打刻を終了できます。タイトルで対象を指定、対象がない場合は無視します。</t>
+    <rPh sb="6" eb="8">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ダコク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーえ」を記入すると、打刻を終了できます。タイトルで対象を指定、対象がない場合は失敗します。</t>
+    <rPh sb="5" eb="7">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ダコク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「ーいたえ」を記入すると、打刻を終了できます。タグで対象を指定、対象がない場合は無視します。</t>
+    <rPh sb="40" eb="42">
+      <t>ムシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日時指定</t>
+    <rPh sb="0" eb="2">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「？」を記入すると、記録日時を指定できます。</t>
+    <rPh sb="4" eb="6">
+      <t>キニュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンからの記録（呼び出し）</t>
+    <rPh sb="6" eb="8">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンからの記録（テンプレート登録）</t>
+    <rPh sb="6" eb="8">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定画面の、「テンプレート構造」ボタンから</t>
+    <rPh sb="0" eb="4">
+      <t>セッテイガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>コウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記録テンプレートボタンを追加できます。</t>
+    <rPh sb="0" eb="2">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フォルダ分けして整理できます。</t>
+    <rPh sb="4" eb="5">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（ドラッグアンドドロップ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ帳記録記法でテンプレート内容に登録</t>
+    <rPh sb="2" eb="3">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモ帳画面から、「テンプレート」ボタンを押すと、</t>
+    <rPh sb="2" eb="3">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録したボタンを呼び出せます。</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面と同様に記録できます。</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終更新日時：2025/11/19 7:26</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウコウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最終更新日時：2025/11/15 7:26</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウコウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1213,8 +1818,26 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1224,12 +1847,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1248,7 +1865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1273,10 +1890,13 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1302,14 +1922,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>86436</xdr:rowOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>86435</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1346,14 +1966,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>89815</xdr:rowOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>89814</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1390,14 +2010,14 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>86061</xdr:rowOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>86060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1434,14 +2054,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>89632</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>89633</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1478,14 +2098,14 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>86062</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>86063</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1522,14 +2142,14 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>2725</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>89816</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>89817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1566,14 +2186,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>286</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>46582</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>34248</xdr:rowOff>
+      <xdr:row>288</xdr:row>
+      <xdr:rowOff>34247</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1610,14 +2230,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>290</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>65635</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>62827</xdr:rowOff>
+      <xdr:row>292</xdr:row>
+      <xdr:rowOff>62828</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1654,13 +2274,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>299</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>56109</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>301</xdr:row>
       <xdr:rowOff>53301</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1698,14 +2318,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>303</xdr:row>
       <xdr:rowOff>-1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>37056</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>62826</xdr:rowOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>62825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1742,14 +2362,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>147</xdr:row>
+      <xdr:row>306</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>37056</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>43775</xdr:rowOff>
+      <xdr:row>308</xdr:row>
+      <xdr:rowOff>43776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1786,14 +2406,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>295</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>84688</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>91406</xdr:rowOff>
+      <xdr:row>297</xdr:row>
+      <xdr:rowOff>91408</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1918,14 +2538,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>245</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>2274</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>1875</xdr:rowOff>
+      <xdr:row>262</xdr:row>
+      <xdr:rowOff>1874</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1962,14 +2582,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>264</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>241147</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>228806</xdr:rowOff>
+      <xdr:row>280</xdr:row>
+      <xdr:rowOff>228807</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2006,13 +2626,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>284</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>241147</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>301</xdr:row>
       <xdr:rowOff>49500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2050,14 +2670,14 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>303</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>241147</xdr:colOff>
-      <xdr:row>161</xdr:row>
-      <xdr:rowOff>49500</xdr:rowOff>
+      <xdr:row>320</xdr:row>
+      <xdr:rowOff>49499</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2094,13 +2714,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>164</xdr:row>
+      <xdr:row>323</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>241147</xdr:colOff>
-      <xdr:row>185</xdr:row>
+      <xdr:row>344</xdr:row>
       <xdr:rowOff>124029</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2138,13 +2758,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>189</xdr:row>
+      <xdr:row>348</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>241147</xdr:colOff>
-      <xdr:row>210</xdr:row>
+      <xdr:row>369</xdr:row>
       <xdr:rowOff>131624</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2182,14 +2802,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>213</xdr:row>
+      <xdr:row>372</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>249441</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>179257</xdr:rowOff>
+      <xdr:row>382</xdr:row>
+      <xdr:rowOff>179258</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2226,13 +2846,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>227</xdr:row>
+      <xdr:row>386</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>249441</xdr:colOff>
-      <xdr:row>237</xdr:row>
+      <xdr:row>396</xdr:row>
       <xdr:rowOff>172081</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2270,14 +2890,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>257735</xdr:colOff>
-      <xdr:row>213</xdr:row>
+      <xdr:row>372</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>249440</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>168284</xdr:rowOff>
+      <xdr:row>382</xdr:row>
+      <xdr:rowOff>168285</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2314,13 +2934,13 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>257735</xdr:colOff>
-      <xdr:row>227</xdr:row>
+      <xdr:row>386</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>249440</xdr:colOff>
-      <xdr:row>237</xdr:row>
+      <xdr:row>396</xdr:row>
       <xdr:rowOff>179675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2358,14 +2978,14 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>257734</xdr:colOff>
-      <xdr:row>213</xdr:row>
+      <xdr:row>372</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>249440</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>183474</xdr:rowOff>
+      <xdr:row>382</xdr:row>
+      <xdr:rowOff>183475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2390,6 +3010,270 @@
         <a:xfrm>
           <a:off x="7989793" y="50336824"/>
           <a:ext cx="3600000" cy="2536709"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>241147</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>213854</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17A08025-4110-97F1-3CF3-7EBC3522F70B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381500" y="13424647"/>
+          <a:ext cx="7200000" cy="6802913"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>186136</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>160244</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1181E6C1-1223-6EEE-A817-A275CA318BEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4416136" y="32800637"/>
+          <a:ext cx="7200000" cy="4524425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>186136</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>150818</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B6E005E-710E-769C-0CAB-B86BB6B5F0E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4416136" y="37407273"/>
+          <a:ext cx="7200000" cy="4515000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>186136</xdr:colOff>
+      <xdr:row>199</xdr:row>
+      <xdr:rowOff>153612</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81F56C8E-1826-67D5-8B38-355CDCBA407E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4416136" y="42013909"/>
+          <a:ext cx="7200000" cy="4517794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>186136</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>67021</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F236165E-9A8D-4EF0-9925-FF4B93266E26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4416136" y="50014909"/>
+          <a:ext cx="7200000" cy="4517794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>220</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>186136</xdr:colOff>
+      <xdr:row>238</xdr:row>
+      <xdr:rowOff>173319</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BE7CAE0-C782-422A-8B16-F6562983C738}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4416136" y="54621545"/>
+          <a:ext cx="7200000" cy="4537500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2730,7 +3614,7 @@
   <sheetData>
     <row r="1" spans="2:29" ht="35.25" x14ac:dyDescent="0.4">
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S1" s="2"/>
     </row>
@@ -2746,187 +3630,187 @@
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.4">
+      <c r="B5" s="8" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.4">
-      <c r="B5" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B29" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B42" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B44" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B49" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2944,7 +3828,802 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AS266"/>
+  <dimension ref="B1:AS425"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="702" width="3.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="703" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:45" ht="35.25" x14ac:dyDescent="0.4">
+      <c r="B1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="AS2" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="AS3" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:45" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:45" x14ac:dyDescent="0.4">
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C28" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C32" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="2:32" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:32" x14ac:dyDescent="0.4">
+      <c r="B56" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="2:32" x14ac:dyDescent="0.4">
+      <c r="B57" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF57" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.4">
+      <c r="B73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF73" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B90" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C92" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D93" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D94" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D95" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D96" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C98" s="10" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D99" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D100" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C102" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D103" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C105" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D106" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C108" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D109" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D110" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="C112" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D113" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="114" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D114" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="116" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="C116" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D117" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="C119" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D120" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="121" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D121" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="122" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D122" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="123" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D123" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="124" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="X124" s="9"/>
+    </row>
+    <row r="125" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="C125" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="126" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D126" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="127" spans="3:24" x14ac:dyDescent="0.4">
+      <c r="D127" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C129" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D130" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D131" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C133" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D134" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="C136" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D137" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D138" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D139" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="D140" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B143" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B145" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B146" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B163" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B164" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B182" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B202" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B204" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B205" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B221" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B245" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B247" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B248" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B250" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B251" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B252" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B255" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B256" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B258" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B260" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B262" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B263" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B264" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B265" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B267" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B269" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B271" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="273" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B273" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="274" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B274" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="275" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B275" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="284" spans="2:5" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B284" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="287" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="E287" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="288" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="E288" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="289" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E289" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="291" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E291" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="292" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E292" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="293" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E293" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="296" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E296" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="297" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E297" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="298" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E298" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="300" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E300" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="301" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E301" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="302" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E302" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="304" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E304" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="305" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E305" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="307" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E307" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="308" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="E308" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B323" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B325" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B326" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B327" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B328" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B330" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B331" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B332" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B333" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B335" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B336" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="347" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B347" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B348" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="371" spans="2:32" x14ac:dyDescent="0.4">
+      <c r="B371" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q371" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF371" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="372" spans="2:32" x14ac:dyDescent="0.4">
+      <c r="B372" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q372" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF372" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="385" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B385" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q385" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="386" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B386" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q386" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="399" spans="2:17" ht="25.5" x14ac:dyDescent="0.4">
+      <c r="B399" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="400" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B400" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B401" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B403" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B404" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B406" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B407" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B408" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B410" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B411" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B412" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B413" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B414" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="415" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B415" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B416" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B417" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B418" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="420" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B420" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B421" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="422" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B422" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B424" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B425" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <rowBreaks count="9" manualBreakCount="9">
+    <brk id="52" max="49" man="1"/>
+    <brk id="88" max="49" man="1"/>
+    <brk id="141" max="49" man="1"/>
+    <brk id="200" max="49" man="1"/>
+    <brk id="243" max="16383" man="1"/>
+    <brk id="282" max="16383" man="1"/>
+    <brk id="321" max="16383" man="1"/>
+    <brk id="345" max="16383" man="1"/>
+    <brk id="397" max="49" man="1"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="47" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F0C4C1-0883-401B-87BA-247F49FE07BA}">
+  <dimension ref="B1:AS8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="702" width="3.375" style="1" bestFit="1" customWidth="1"/>
@@ -2959,7 +4638,7 @@
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.4">
       <c r="AS2" s="3" t="s">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.4">
@@ -2967,545 +4646,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:45" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="D7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="D10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C25" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C27" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C29" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C31" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C32" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="53" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B53" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B54" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF54" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF70" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B87" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B89" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B90" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B92" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B93" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B94" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B97" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B98" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B100" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B102" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B104" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B105" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B106" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B107" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B109" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B111" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B113" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B115" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B116" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B117" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B125" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="E128" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E129" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E130" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E132" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E133" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E134" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E137" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E138" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E139" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E141" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E142" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E143" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E145" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E146" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E148" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E149" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B164" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B166" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B167" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B168" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B169" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B171" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B172" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B173" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B174" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B176" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B177" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B188" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B189" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="212" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B212" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q212" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF212" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="213" spans="2:32" x14ac:dyDescent="0.4">
-      <c r="B213" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q213" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF213" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="226" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B226" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q226" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="227" spans="2:17" x14ac:dyDescent="0.4">
-      <c r="B227" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q227" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="240" spans="2:17" ht="25.5" x14ac:dyDescent="0.4">
-      <c r="B240" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B241" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B242" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="244" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B244" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B245" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B247" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B248" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B249" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B251" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B252" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B253" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="254" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B254" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B255" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="256" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B256" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B257" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B258" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B259" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B261" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B262" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B263" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B265" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B266" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <rowBreaks count="6" manualBreakCount="6">
-    <brk id="52" max="16383" man="1"/>
-    <brk id="86" max="16383" man="1"/>
-    <brk id="124" max="16383" man="1"/>
-    <brk id="163" max="16383" man="1"/>
-    <brk id="187" max="16383" man="1"/>
-    <brk id="239" max="16383" man="1"/>
-  </rowBreaks>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="69" man="1"/>
-  </colBreaks>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F0C4C1-0883-401B-87BA-247F49FE07BA}">
-  <dimension ref="B1:AS10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="702" width="3.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="703" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:45" ht="35.25" x14ac:dyDescent="0.4">
-      <c r="B1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="S1" s="2"/>
-    </row>
-    <row r="2" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="AS2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="AS3" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="5" spans="2:45" x14ac:dyDescent="0.4">
       <c r="B5" s="5" t="s">
         <v>47</v>
@@ -3525,14 +4665,6 @@
       <c r="B8" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/documents/gkill_user_document.xlsx
+++ b/documents/gkill_user_document.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamat\Git\gkill\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4295784-08AA-442D-91B1-5F7B6B3FFD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B0DDCA-1A4B-4068-A39B-D42269395094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{231E213C-47DE-4CA2-9B9F-8072DD02A1E6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{231E213C-47DE-4CA2-9B9F-8072DD02A1E6}"/>
   </bookViews>
   <sheets>
     <sheet name="導入" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="189">
   <si>
     <t>最終更新日時：2025/11/15 15:45</t>
     <rPh sb="0" eb="4">
@@ -541,40 +541,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>タスクのチェックがうごかないです？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ライフログビューの検索結果リストからはできません。</t>
-    <rPh sb="9" eb="13">
-      <t>ケンサクケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スマホ操作時に誤チェックが多発したためです。</t>
-    <rPh sb="3" eb="5">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>アヤマ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>タハツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダブルクリックしてダイアログからチェックを入れてください。</t>
-    <rPh sb="21" eb="22">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>状況確認と情報記録用の画面。</t>
     <rPh sb="0" eb="2">
       <t>ジョウキョウ</t>
@@ -1742,7 +1708,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>最終更新日時：2025/11/15 7:26</t>
+    <t>最終更新日時：2025/11/26 5:38</t>
     <rPh sb="0" eb="4">
       <t>サイシュウコウシン</t>
     </rPh>
@@ -3614,7 +3580,7 @@
   <sheetData>
     <row r="1" spans="2:29" ht="35.25" x14ac:dyDescent="0.4">
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="S1" s="2"/>
     </row>
@@ -3630,187 +3596,187 @@
     </row>
     <row r="4" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B5" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="2:29" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B27" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B29" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B40" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B41" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B42" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B43" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B44" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B46" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B47" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B48" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B49" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3837,13 +3803,13 @@
   <sheetData>
     <row r="1" spans="2:45" ht="35.25" x14ac:dyDescent="0.4">
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S1" s="2"/>
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.4">
       <c r="AS2" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.4">
@@ -3893,7 +3859,7 @@
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
@@ -3903,22 +3869,22 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="2:32" ht="25.5" x14ac:dyDescent="0.4">
@@ -3955,82 +3921,82 @@
     </row>
     <row r="90" spans="2:4" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B90" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C92" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D93" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D94" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D95" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D96" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="98" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C98" s="10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D99" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D100" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="102" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C102" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D103" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="105" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C105" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D106" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="108" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C108" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D109" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D110" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="112" spans="3:4" x14ac:dyDescent="0.4">
@@ -4040,12 +4006,12 @@
     </row>
     <row r="113" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D113" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D114" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="116" spans="3:24" x14ac:dyDescent="0.4">
@@ -4055,7 +4021,7 @@
     </row>
     <row r="117" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D117" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="119" spans="3:24" x14ac:dyDescent="0.4">
@@ -4065,22 +4031,22 @@
     </row>
     <row r="120" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D120" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="121" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D121" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="122" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D122" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="123" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D123" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124" spans="3:24" x14ac:dyDescent="0.4">
@@ -4088,17 +4054,17 @@
     </row>
     <row r="125" spans="3:24" x14ac:dyDescent="0.4">
       <c r="C125" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="126" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D126" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="127" spans="3:24" x14ac:dyDescent="0.4">
       <c r="D127" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.4">
@@ -4108,97 +4074,97 @@
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D130" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D131" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C133" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D134" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C136" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D137" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D138" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D139" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.4">
       <c r="D140" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="2:4" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B143" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B145" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="146" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B146" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B163" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="164" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B164" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="182" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B182" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="202" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B202" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="204" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B204" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="205" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B205" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="221" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B221" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="245" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
@@ -4253,22 +4219,22 @@
     </row>
     <row r="262" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B262" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="263" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B263" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="264" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B264" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="265" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B265" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="267" spans="2:2" x14ac:dyDescent="0.4">
@@ -4288,12 +4254,12 @@
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B273" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B274" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.4">
@@ -4303,7 +4269,7 @@
     </row>
     <row r="284" spans="2:5" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B284" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.4">
@@ -4313,12 +4279,12 @@
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E288" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="289" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E289" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="291" spans="5:5" x14ac:dyDescent="0.4">
@@ -4328,27 +4294,27 @@
     </row>
     <row r="292" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E292" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="293" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E293" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="296" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E296" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="297" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E297" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="298" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E298" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="300" spans="5:5" x14ac:dyDescent="0.4">
@@ -4358,12 +4324,12 @@
     </row>
     <row r="301" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E301" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="302" spans="5:5" x14ac:dyDescent="0.4">
       <c r="E302" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="304" spans="5:5" x14ac:dyDescent="0.4">
@@ -4388,57 +4354,57 @@
     </row>
     <row r="323" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B323" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="325" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B325" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="326" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B326" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="327" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B327" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="328" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B328" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="330" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B330" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="331" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B331" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="332" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B332" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="333" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B333" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="335" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B335" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="336" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B336" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="347" spans="2:2" ht="25.5" x14ac:dyDescent="0.4">
@@ -4470,7 +4436,7 @@
         <v>46</v>
       </c>
       <c r="AF372" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="385" spans="2:17" x14ac:dyDescent="0.4">
@@ -4483,126 +4449,126 @@
     </row>
     <row r="386" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B386" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q386" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="399" spans="2:17" ht="25.5" x14ac:dyDescent="0.4">
       <c r="B399" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="400" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B400" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="401" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B401" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="403" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B403" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="404" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B404" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="406" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B406" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="407" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B407" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="408" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B408" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="410" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B410" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="411" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B411" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="412" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B412" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="413" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B413" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="414" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B414" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="415" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B415" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="416" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B416" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="417" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B417" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="418" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B418" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="420" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B420" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="421" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B421" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="422" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B422" s="7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="424" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B424" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="425" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B425" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <rowBreaks count="9" manualBreakCount="9">
     <brk id="52" max="49" man="1"/>
     <brk id="88" max="49" man="1"/>
@@ -4623,7 +4589,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F0C4C1-0883-401B-87BA-247F49FE07BA}">
-  <dimension ref="B1:AS8"/>
+  <dimension ref="B1:AS5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="702" width="3.375" style="1" bestFit="1" customWidth="1"/>
@@ -4632,13 +4598,13 @@
   <sheetData>
     <row r="1" spans="2:45" ht="35.25" x14ac:dyDescent="0.4">
       <c r="B1" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="S1" s="2"/>
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.4">
       <c r="AS2" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.4">
@@ -4647,24 +4613,7 @@
       </c>
     </row>
     <row r="5" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="B5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="2:45" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="B5" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
